--- a/deliverables/GPT56_SOL_SECTION32_MULTI_TRACT_SPRINT_20260716/GPT56_SOL_SECTION32_RUNSHEET_20260716.xlsx
+++ b/deliverables/GPT56_SOL_SECTION32_MULTI_TRACT_SPRINT_20260716/GPT56_SOL_SECTION32_RUNSHEET_20260716.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Runsheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runsheet'!$A$1:$Z$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runsheet'!$A$1:$Z$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -446,19 +446,19 @@
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
     <col width="42" customWidth="1" min="12" max="12"/>
     <col width="42" customWidth="1" min="13" max="13"/>
     <col width="42" customWidth="1" min="14" max="14"/>
     <col width="42" customWidth="1" min="15" max="15"/>
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="25" customWidth="1" min="18" max="18"/>
-    <col width="35" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="42" customWidth="1" min="19" max="19"/>
     <col width="42" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="27" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="42" customWidth="1" min="23" max="23"/>
     <col width="42" customWidth="1" min="24" max="24"/>
@@ -820,10 +820,14 @@
           <t>1947-11-13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1947-11-26</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>OGL REF</t>
+          <t>OGL</t>
         </is>
       </c>
       <c r="F4" s="2" t="n"/>
@@ -834,10 +838,14 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Cora B. Garrett; S.A. Garrett</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n"/>
+          <t>Cora B. Garrett; S.A. Garrett, her husband</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Mayfield, Oklahoma</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>C.E. McKinley</t>
@@ -855,7 +863,11 @@
         </is>
       </c>
       <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Historic leasehold face; 1/8 royalty; 10-year primary term</t>
+        </is>
+      </c>
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="2" t="inlineStr">
         <is>
@@ -869,36 +881,36 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>DIRECT-IMAGE ASSIGNMENT RECITAL</t>
+          <t>DIRECT ORIGINAL IMAGE + RECORDED ASSIGNMENT EXHIBITS</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>Bk 244/Pg 432 / Image 1062; Bk 872/Pg 284 / Image 4393</t>
+          <t>OGL 63/33 / Image 0353; Bk 244/Pg 432 / Image 1062; Bk 872/Pg 284 / Image 4393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>Images 1062, 4393</t>
+          <t>Images 0353, 1062, 4393</t>
         </is>
       </c>
       <c r="V4" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>Historic lease identity only</t>
+          <t>Historic lease terms and identity only</t>
         </is>
       </c>
       <c r="X4" s="2" t="n"/>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>Pull original OGL and all amendments/releases</t>
+          <t>Pull amendments, ratifications, releases, pooling, production, and HBP evidence</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>Royalty, term, clauses, depth, expiration, and HBP remain open.</t>
+          <t>Original face proves 1/8 royalty and 10-year term. Pooling and shut-in clauses are present but current effect, continuation, and HBP remain open.</t>
         </is>
       </c>
     </row>
@@ -1265,13 +1277,21 @@
           <t>Union Oil Company of California</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>P. O. Box 3100, Midland, Texas 79702</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Leede Exploration</t>
         </is>
       </c>
-      <c r="K8" s="2" t="n"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>600 North Marienfeld, Midland, Texas 79701</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Listed Section 32 leases; E/2 SE/4 specially limited</t>
@@ -1381,13 +1401,21 @@
           <t>Consolidation of Leede Trusts</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>600 North Marienfeld, Midland, Texas 79701</t>
+        </is>
+      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Leede Exploration</t>
         </is>
       </c>
-      <c r="K9" s="2" t="n"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>600 North Marienfeld, Midland, Texas 79701</t>
+        </is>
+      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
           <t>N/2 Section 32</t>
@@ -1403,7 +1431,11 @@
           <t>All depths below top Hunton</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>All assignor right, title, and interest in OGLs and other working/cost-bearing interests; effective for all purposes as of first production from McCall #1-29</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
           <t>Royalty/ORRI reconveyance effect unclear</t>
@@ -1595,7 +1627,11 @@
           <t>Diversified Production LLC</t>
         </is>
       </c>
-      <c r="K11" s="2" t="n"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1600 Corporate Drive, Birmingham, AL 35242</t>
+        </is>
+      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Section 32 schedule reference; asset OK48147.001.1</t>
@@ -1654,8 +1690,1120 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>T1,T4</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1972-02-05</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1972-02-22</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>OGL</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>264/345</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Charlie B. Crook; Ima Pearl Crook, his wife</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Route 1, Mayfield, Oklahoma</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Union Oil Company of California</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>NE/4</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Historic leasehold</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Royalty 1/8; primary term 5 years commencing 1973-01-13</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>264/345</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>Union/Leede deep package</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT ORIGINAL IMAGE + RECORDED EXHIBIT</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>Images 1197–1198 and 4392. Instrument also covers 80 acres in Section 28; only 160 Section 32 row acres counted.</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>Images 1197–1198 and 4392</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Historic original lease facts only; current status OPEN</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="n"/>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>Confirm clerk metadata; acquire amendments, corrections, releases, pooling, and HBP evidence</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>Later Bk 872/Pg 279 depth and ORRI terms apply only to that assignment; they are not original-lease terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1976-04-29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1976-06-09</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>OGL</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2991</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>307/31</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Cora B. LeGrand, widow</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Sweetwater, Oklahoma</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Union Oil Company of California</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>W/2 SE/4 and S/2 SW/4</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Historic leasehold</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Royalty 1/8; primary term 5 years commencing 1976-09-23</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>307/31</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>Union/Leede deep package</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT ORIGINAL IMAGE + RECORDED EXHIBIT</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>Images 1372 and 4391. Overlaps other listed rows; no present status or HBP inference.</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>Images 1372 and 4391</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Historic original lease facts only; current status OPEN</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="n"/>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>Confirm clerk metadata; acquire amendments, corrections, releases, pooling, and HBP evidence</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>Later Bk 872/Pg 279 depth and ORRI terms apply only to that assignment; they are not original-lease terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1977-10-14</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>OGL</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>340/302</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Gertrude L. LaFortune; Jeanne L. Fair; Mary Ann L. Wilcox; J.A. LaFortune Jr.; Robert J. LaFortune, co-trustees under the will of Joseph A. LaFortune</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2300 Fourth National Bank Building, Tulsa, Oklahoma</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Union Oil Company of California</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>N/2 SW/4</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Historic leasehold</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Royalty 3/16; primary term 5 years commencing 1977-11-28</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>340/302</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Union/Leede deep package</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT ORIGINAL IMAGE + RECORDED EXHIBIT</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>Images 1522–1523 and 4391. Relationship to separate 340/304 remains open.</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>Images 1522–1523 and 4391</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Historic original lease facts only; current status OPEN</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="n"/>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>Confirm clerk metadata; acquire amendments, corrections, releases, pooling, and HBP evidence</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>Later Bk 872/Pg 279 depth and ORRI terms apply only to that assignment; they are not original-lease terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1977-10-14</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>OGL</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>340/304</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Gertrude LaFortune, widow</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2300 Fourth National Building, Tulsa, Oklahoma 74119</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Union Oil Company of California</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>N/2 SW/4</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Historic leasehold</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Royalty 3/16; primary term 5 years commencing 1977-11-28</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>340/304</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>Union/Leede deep package</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT ORIGINAL IMAGE + RECORDED EXHIBIT</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>Images 1524–1525 and 4391. Separate overlapping lease; do not double count.</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>Images 1524–1525 and 4391</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Historic original lease facts only; current status OPEN</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="n"/>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>Confirm clerk metadata; acquire amendments, corrections, releases, pooling, and HBP evidence</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>Later Bk 872/Pg 279 depth and ORRI terms apply only to that assignment; they are not original-lease terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1977-09-29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1977-11-07</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>OGL</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>340/323</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>George T. Harrison Jr.; Renata Harrison</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>201 North Charles Street, Baltimore, Maryland 21201</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Union Oil Company of California</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>N/2 NW/4 and N/2 SW/4</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Historic leasehold</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Royalty 3/16; primary term 5 years commencing 1977-11-27</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>340/323</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>Union/Leede deep package</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT ORIGINAL IMAGE + RECORDED EXHIBIT</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>Images 1526–1527 and 4391. This is the only listed lease aliquot covering N/2 NW/4.</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>Images 1526–1527 and 4391</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Historic original lease facts only; current status OPEN</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="n"/>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>Confirm clerk metadata; acquire amendments, corrections, releases, pooling, and HBP evidence</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>Later Bk 872/Pg 279 depth and ORRI terms apply only to that assignment; they are not original-lease terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1977-09-29</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1978-02-09</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>OGL</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1089</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>342/564</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Carol Seidenbach Leach</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>c/o Mrs. J. Leslie Seidenbach, 2827 South Birmingham Place, Tulsa, Oklahoma</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Union Oil Company of California</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>N/2 SW/4</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Historic leasehold</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Royalty 3/16; primary term 5 years commencing 1977-11-30</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>342/564</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Union/Leede deep package</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT ORIGINAL IMAGE + RECORDED EXHIBIT</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>Images 1542–1543 and 4391. Overlapping legal; current status open.</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>Images 1542–1543 and 4391</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Historic original lease facts only; current status OPEN</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="n"/>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>Confirm clerk metadata; acquire amendments, corrections, releases, pooling, and HBP evidence</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>Later Bk 872/Pg 279 depth and ORRI terms apply only to that assignment; they are not original-lease terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1977-11-01</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1978-02-09</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>OGL</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1090</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>342/566</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Cynthia Seidenbach Kruse</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>c/o M. B. Johnson, 1623 S. College, Tulsa, Oklahoma 74104</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Union Oil Company of California</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>N/2 SW/4</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Historic leasehold</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Royalty 3/16; primary term 5 years commencing 1977-11-30</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="n"/>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>342/566</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Union/Leede deep package</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT ORIGINAL IMAGE + RECORDED EXHIBIT</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>Images 1544–1545 and 4391. Overlapping legal; current status open.</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>Images 1544–1545 and 4391</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Historic original lease facts only; current status OPEN</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="n"/>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>Confirm clerk metadata; acquire amendments, corrections, releases, pooling, and HBP evidence</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>Later Bk 872/Pg 279 depth and ORRI terms apply only to that assignment; they are not original-lease terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>T1,T4</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1978-05-16</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1978-06-27</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>OGL</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>352/719</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>F.L. Randel</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>P. O. Box 7, c/o Ramada Inn, Big Spring, Texas 79720</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Union Oil Company of California</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>NE/4</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Historic leasehold</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Royalty 3/16; primary term 5 years</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="n"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>352/719</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Union/Leede deep package</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT ORIGINAL IMAGE + RECORDED EXHIBIT</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>Images 1552–1553 and 4391. Face instrument 5169 conflicts with protocol index 5051; clerk confirmation required.</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>Images 1552–1553 and 4391</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Historic original lease facts only; current status OPEN</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>Direct face instrument 5169 conflicts with protocol index 5051</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>Confirm clerk metadata; acquire amendments, corrections, releases, pooling, and HBP evidence</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>Later Bk 872/Pg 279 depth and ORRI terms apply only to that assignment; they are not original-lease terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>T1,T4</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1978-05-16</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1978-06-27</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>OGL</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>352/721</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>J.L. Randel</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Box 2609, Wichita Falls, Texas</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Union Oil Company of California</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>NE/4</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Historic leasehold</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Royalty 3/16; primary term 5 years</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>352/721</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>Union/Leede deep package</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT ORIGINAL IMAGE + RECORDED EXHIBIT</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>Images 1554–1555 and 4392. Face instrument 5168 conflicts with protocol index 5052; clerk confirmation required.</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>Images 1554–1555 and 4392</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>Historic original lease facts only; current status OPEN</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>Direct face instrument 5168 conflicts with protocol index 5052</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>Confirm clerk metadata; acquire amendments, corrections, releases, pooling, and HBP evidence</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>Later Bk 872/Pg 279 depth and ORRI terms apply only to that assignment; they are not original-lease terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>T1,T4</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>1979-03-21</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1979-04-30</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>OGL</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>3757</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>376/369</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Great Western Oil &amp; Gas, Inc., a California corporation</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>4010 Palos Verdes Drive North, Suite 206, Rolling Hills Estates, California 90274</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Union Oil Company of California</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>NE/4</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Historic leasehold</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Royalty 3/16; primary term 5 years</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>376/369</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>Union/Leede deep package</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>DIRECT ORIGINAL IMAGE + RECORDED EXHIBIT</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>Images 1569–1570 and 4392. Face instrument 3757 conflicts with protocol index 3707; correction metadata at 1039/20–23 remains unreviewed.</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>Images 1569–1570 and 4392</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>Historic original lease facts only; current status OPEN</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>Direct face instrument 3757 conflicts with protocol index 3707</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>Confirm clerk metadata; acquire amendments, corrections, releases, pooling, and HBP evidence</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>Later Bk 872/Pg 279 depth and ORRI terms apply only to that assignment; they are not original-lease terms.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z11"/>
+  <autoFilter ref="A1:Z21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>